--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{FE88551D-BD51-364E-8A4D-797DCEB10DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C65B4E0-2469-AC45-92ED-E921C8E8F04B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="57">
   <si>
     <t>Atleta</t>
   </si>
@@ -183,6 +183,38 @@
   </si>
   <si>
     <t>Erik Lopez</t>
+  </si>
+  <si>
+    <t>SEDE
+Tlaxcala Tlaxcala</t>
+  </si>
+  <si>
+    <t>SEDE
+CDMX</t>
+  </si>
+  <si>
+    <t>SEDE
+KIDS CENTER</t>
+  </si>
+  <si>
+    <t>SEDE
+Sarasota Florida</t>
+  </si>
+  <si>
+    <t>SEDE
+Por definir</t>
+  </si>
+  <si>
+    <t>SEDE
+Puebla Puebla</t>
+  </si>
+  <si>
+    <t>SEDE
+Guadalajara Jalisco</t>
+  </si>
+  <si>
+    <t>SEDE
+Estado de Mexico</t>
   </si>
 </sst>
 </file>
@@ -225,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -248,12 +280,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -273,54 +331,18 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -673,7 +695,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -684,10 +706,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -727,54 +749,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="5">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" s="6">
-        <f>COUNTIF(C2:M2,"SI")/7</f>
-        <v>0.8571428571428571</v>
-      </c>
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -813,16 +828,16 @@
         <v>5</v>
       </c>
       <c r="N3" s="6">
-        <f>COUNTIF(C3:M3,"SI")/7</f>
+        <f t="shared" ref="N3:N20" si="0">COUNTIF(C3:M3,"SI")/7</f>
         <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -849,25 +864,25 @@
         <v>4</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="N4" s="6">
-        <f>COUNTIF(C4:M4,"SI")/7</f>
-        <v>1.1428571428571428</v>
+        <f t="shared" si="0"/>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -903,13 +918,13 @@
         <v>5</v>
       </c>
       <c r="N5" s="6">
-        <f>COUNTIF(C5:M5,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
@@ -948,13 +963,13 @@
         <v>5</v>
       </c>
       <c r="N6" s="6">
-        <f>COUNTIF(C6:M6,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5">
         <v>5</v>
@@ -993,13 +1008,13 @@
         <v>5</v>
       </c>
       <c r="N7" s="6">
-        <f>COUNTIF(C7:M7,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
         <v>5</v>
@@ -1038,13 +1053,13 @@
         <v>5</v>
       </c>
       <c r="N8" s="6">
-        <f>COUNTIF(C8:M8,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5">
         <v>5</v>
@@ -1083,13 +1098,13 @@
         <v>5</v>
       </c>
       <c r="N9" s="6">
-        <f>COUNTIF(C9:M9,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5">
         <v>5</v>
@@ -1128,13 +1143,13 @@
         <v>5</v>
       </c>
       <c r="N10" s="6">
-        <f>COUNTIF(C10:M10,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5">
         <v>5</v>
@@ -1173,13 +1188,13 @@
         <v>5</v>
       </c>
       <c r="N11" s="6">
-        <f>COUNTIF(C11:M11,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5">
         <v>5</v>
@@ -1218,13 +1233,13 @@
         <v>5</v>
       </c>
       <c r="N12" s="6">
-        <f>COUNTIF(C12:M12,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5">
         <v>5</v>
@@ -1263,13 +1278,13 @@
         <v>5</v>
       </c>
       <c r="N13" s="6">
-        <f>COUNTIF(C13:M13,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5">
         <v>5</v>
@@ -1308,13 +1323,13 @@
         <v>5</v>
       </c>
       <c r="N14" s="6">
-        <f>COUNTIF(C14:M14,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B15" s="5">
         <v>5</v>
@@ -1353,13 +1368,13 @@
         <v>5</v>
       </c>
       <c r="N15" s="6">
-        <f>COUNTIF(C15:M15,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5">
         <v>5</v>
@@ -1398,16 +1413,16 @@
         <v>5</v>
       </c>
       <c r="N16" s="6">
-        <f>COUNTIF(C16:M16,"SI")/7</f>
+        <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1440,19 +1455,19 @@
         <v>4</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="6">
-        <f>COUNTIF(C17:M17,"SI")/7</f>
-        <v>1.2857142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -1485,19 +1500,19 @@
         <v>4</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" s="6">
-        <f>COUNTIF(C18:M18,"SI")/7</f>
-        <v>1.1428571428571428</v>
+        <f t="shared" si="0"/>
+        <v>1.2857142857142858</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -1530,16 +1545,16 @@
         <v>4</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" s="6">
-        <f>COUNTIF(C19:M19,"SI")/7</f>
-        <v>1.2857142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="5">
         <v>8</v>
@@ -1578,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6">
-        <f>COUNTIF(C20:M20,"SI")/8</f>
-        <v>1.125</v>
+        <f t="shared" si="0"/>
+        <v>1.2857142857142858</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B21" s="5">
         <v>8</v>
@@ -1623,13 +1638,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6">
-        <f>COUNTIF(C21:M21,"SI")/7</f>
-        <v>1.2857142857142858</v>
+        <f>COUNTIF(C21:M21,"SI")/8</f>
+        <v>1.125</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5">
         <v>8</v>
@@ -1674,10 +1689,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1692,13 +1707,13 @@
         <v>4</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -1714,12 +1729,12 @@
       </c>
       <c r="N23" s="6">
         <f>COUNTIF(C23:M23,"SI")/7</f>
-        <v>1.5714285714285714</v>
+        <v>1.2857142857142858</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B24" s="5">
         <v>9</v>
@@ -1755,16 +1770,16 @@
         <v>4</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24" s="6">
         <f>COUNTIF(C24:M24,"SI")/7</f>
-        <v>1.4285714285714286</v>
+        <v>1.5714285714285714</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5">
         <v>9</v>
@@ -1782,13 +1797,13 @@
         <v>4</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>4</v>
@@ -1800,16 +1815,16 @@
         <v>4</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N25" s="6">
-        <f>COUNTIF(C25:M25,"SI")/8</f>
-        <v>1.125</v>
+        <f>COUNTIF(C25:M25,"SI")/7</f>
+        <v>1.4285714285714286</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B26" s="5">
         <v>9</v>
@@ -1827,13 +1842,13 @@
         <v>4</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>4</v>
@@ -1849,12 +1864,12 @@
       </c>
       <c r="N26" s="6">
         <f>COUNTIF(C26:M26,"SI")/8</f>
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5">
         <v>9</v>
@@ -1899,10 +1914,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B28" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1938,13 +1953,13 @@
         <v>4</v>
       </c>
       <c r="N28" s="6">
-        <f>COUNTIF(C28:M28,"SI")/10</f>
-        <v>1.1000000000000001</v>
+        <f>COUNTIF(C28:M28,"SI")/8</f>
+        <v>1.375</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B29" s="5">
         <v>10</v>
@@ -1989,10 +2004,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="B30" s="5">
+        <v>10</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -2025,28 +2040,28 @@
         <v>4</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" s="6">
         <f>COUNTIF(C30:M30,"SI")/10</f>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>4</v>
@@ -2055,13 +2070,13 @@
         <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>4</v>
@@ -2073,25 +2088,25 @@
         <v>5</v>
       </c>
       <c r="N31" s="6">
-        <f>COUNTIF(C31:M31,"SI")/9</f>
-        <v>0.55555555555555558</v>
+        <f>COUNTIF(C31:M31,"SI")/10</f>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>4</v>
@@ -2100,13 +2115,13 @@
         <v>4</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>4</v>
@@ -2119,56 +2134,83 @@
       </c>
       <c r="N32" s="6">
         <f>COUNTIF(C32:M32,"SI")/9</f>
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="6">
+        <f>COUNTIF(C33:M33,"SI")/9</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:N32">
-    <sortCondition ref="B1:B32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:N33">
+    <sortCondition ref="B1:B33"/>
   </sortState>
-  <conditionalFormatting sqref="C5:M32">
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="No aplica">
-      <formula>NOT(ISERROR(SEARCH("No aplica",C5)))</formula>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3:M33">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="No aplica">
+      <formula>NOT(ISERROR(SEARCH("No aplica",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",C5)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="SI">
-      <formula>NOT(ISERROR(SEARCH("SI",C5)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="SI">
+      <formula>NOT(ISERROR(SEARCH("SI",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N32">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="N3:N33">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>0.85</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="8" stopIfTrue="1" operator="between">
       <formula>0.7</formula>
       <formula>0.84999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0.69999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:M4">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="No aplica">
-      <formula>NOT(ISERROR(SEARCH("No aplica",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="SI">
-      <formula>NOT(ISERROR(SEARCH("SI",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:M2">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="No aplica">
-      <formula>NOT(ISERROR(SEARCH("No aplica",C2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",C2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="SI">
-      <formula>NOT(ISERROR(SEARCH("SI",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E9272B-26B2-7B47-99B5-A5B1E8B51B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="58">
   <si>
     <t>Atleta</t>
   </si>
@@ -215,6 +215,9 @@
   <si>
     <t>SEDE
 Estado de Mexico</t>
+  </si>
+  <si>
+    <t>Por Definir</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="1" customWidth="1"/>
     <col min="3" max="13" width="12.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
@@ -1061,8 +1064,8 @@
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5">
-        <v>5</v>
+      <c r="B9" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1196,8 +1199,8 @@
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="5">
-        <v>5</v>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E9272B-26B2-7B47-99B5-A5B1E8B51B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC171D10-4A71-954B-982F-549CB9B1F0FA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -217,7 +217,7 @@
 Estado de Mexico</t>
   </si>
   <si>
-    <t>Por Definir</t>
+    <t>Por definir</t>
   </si>
 </sst>
 </file>
@@ -699,16 +699,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="12.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="10.76171875" style="1" customWidth="1"/>
+    <col min="3" max="13" width="12.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.01171875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -752,7 +752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
@@ -790,7 +790,7 @@
       </c>
       <c r="N2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>46</v>
       </c>
@@ -831,11 +831,11 @@
         <v>5</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" ref="N3:N20" si="0">COUNTIF(C3:M3,"SI")/7</f>
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C3:M3,"SI")/6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
@@ -876,11 +876,11 @@
         <v>5</v>
       </c>
       <c r="N4" s="6">
-        <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C4:M4,"SI")/6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
@@ -921,11 +921,11 @@
         <v>5</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C5:M5,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -966,11 +966,11 @@
         <v>5</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C6:M6,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1011,11 +1011,11 @@
         <v>5</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C7:M7,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1056,11 +1056,11 @@
         <v>5</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C8:M8,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1101,11 +1101,11 @@
         <v>5</v>
       </c>
       <c r="N9" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C9:M9,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1146,11 +1146,11 @@
         <v>5</v>
       </c>
       <c r="N10" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C10:M10,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1191,11 +1191,11 @@
         <v>5</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C11:M11,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1236,11 +1236,11 @@
         <v>5</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C12:M12,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
@@ -1281,11 +1281,11 @@
         <v>5</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C13:M13,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1326,11 +1326,11 @@
         <v>5</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C14:M14,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
@@ -1371,11 +1371,11 @@
         <v>5</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C15:M15,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
@@ -1416,11 +1416,11 @@
         <v>5</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C16:M16,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
@@ -1461,11 +1461,11 @@
         <v>5</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C17:M17,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -1506,11 +1506,11 @@
         <v>4</v>
       </c>
       <c r="N18" s="6">
-        <f t="shared" si="0"/>
-        <v>1.2857142857142858</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C18:M18,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -1551,11 +1551,11 @@
         <v>5</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C19:M19,"SI")/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -1596,11 +1596,11 @@
         <v>4</v>
       </c>
       <c r="N20" s="6">
-        <f t="shared" si="0"/>
-        <v>1.2857142857142858</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C20:M20,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
@@ -1641,11 +1641,11 @@
         <v>4</v>
       </c>
       <c r="N21" s="6">
-        <f>COUNTIF(C21:M21,"SI")/8</f>
-        <v>1.125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C21:M21,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -1686,11 +1686,11 @@
         <v>4</v>
       </c>
       <c r="N22" s="6">
-        <f>COUNTIF(C22:M22,"SI")/7</f>
-        <v>1.2857142857142858</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C22:M22,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>31</v>
       </c>
@@ -1731,11 +1731,11 @@
         <v>4</v>
       </c>
       <c r="N23" s="6">
-        <f>COUNTIF(C23:M23,"SI")/7</f>
-        <v>1.2857142857142858</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C23:M23,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>9</v>
       </c>
@@ -1776,11 +1776,11 @@
         <v>4</v>
       </c>
       <c r="N24" s="6">
-        <f>COUNTIF(C24:M24,"SI")/7</f>
-        <v>1.5714285714285714</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C24:M24,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -1821,11 +1821,11 @@
         <v>5</v>
       </c>
       <c r="N25" s="6">
-        <f>COUNTIF(C25:M25,"SI")/7</f>
-        <v>1.4285714285714286</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C25:M25,"SI")/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -1866,11 +1866,11 @@
         <v>4</v>
       </c>
       <c r="N26" s="6">
-        <f>COUNTIF(C26:M26,"SI")/8</f>
-        <v>1.125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C26:M26,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
@@ -1911,11 +1911,11 @@
         <v>4</v>
       </c>
       <c r="N27" s="6">
-        <f>COUNTIF(C27:M27,"SI")/8</f>
-        <v>1.375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C27:M27,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>29</v>
       </c>
@@ -1956,11 +1956,11 @@
         <v>4</v>
       </c>
       <c r="N28" s="6">
-        <f>COUNTIF(C28:M28,"SI")/8</f>
-        <v>1.375</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C28:M28,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
@@ -2001,11 +2001,11 @@
         <v>4</v>
       </c>
       <c r="N29" s="6">
-        <f>COUNTIF(C29:M29,"SI")/10</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C29:M29,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>12</v>
       </c>
@@ -2046,11 +2046,11 @@
         <v>4</v>
       </c>
       <c r="N30" s="6">
-        <f>COUNTIF(C30:M30,"SI")/10</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C30:M30,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -2136,11 +2136,11 @@
         <v>5</v>
       </c>
       <c r="N32" s="6">
-        <f>COUNTIF(C32:M32,"SI")/9</f>
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C32:M32,"SI")/5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -2181,8 +2181,8 @@
         <v>5</v>
       </c>
       <c r="N33" s="6">
-        <f>COUNTIF(C33:M33,"SI")/9</f>
-        <v>1.1111111111111112</v>
+        <f>COUNTIF(C33:M33,"SI")/10</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC171D10-4A71-954B-982F-549CB9B1F0FA}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01BD6C6A-B252-734B-B074-4482B5C3E542}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="64">
   <si>
     <t>Atleta</t>
   </si>
@@ -141,18 +141,6 @@
   </si>
   <si>
     <t>COPA ACTION GYM 26</t>
-  </si>
-  <si>
-    <t>COPA BENITO JUAREZ 2</t>
-  </si>
-  <si>
-    <t>CTRL DE ENERO</t>
-  </si>
-  <si>
-    <t>MIKULAK INVITATIONAL CUP 2027</t>
-  </si>
-  <si>
-    <t>SELECTIVO NACIONAL 2027</t>
   </si>
   <si>
     <t>AGEPAC 27</t>
@@ -218,6 +206,25 @@
   </si>
   <si>
     <t>Por definir</t>
+  </si>
+  <si>
+    <t>CONTROL SIN JUEZ</t>
+  </si>
+  <si>
+    <t>COPA DANIEL CORRAL 27</t>
+  </si>
+  <si>
+    <t>SEDE
+Monterrey Nuevo Leon</t>
+  </si>
+  <si>
+    <t>COPA BENITO JUAREZ 26</t>
+  </si>
+  <si>
+    <t>MIKULAK INVITATIONAL CUP 27</t>
+  </si>
+  <si>
+    <t>SELECTIVO NACIONAL 27</t>
   </si>
 </sst>
 </file>
@@ -698,17 +705,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.76171875" style="1" customWidth="1"/>
-    <col min="3" max="13" width="12.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.01171875" style="1"/>
+    <col min="3" max="14" width="12.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.01171875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -719,80 +726,86 @@
         <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="M2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -830,14 +843,17 @@
       <c r="M3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="6">
-        <f>COUNTIF(C3:M3,"SI")/6</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="6">
+        <f>COUNTIF(C3:N3,"SI")/6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -875,14 +891,17 @@
       <c r="M4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="6">
-        <f>COUNTIF(C4:M4,"SI")/6</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="6">
+        <f>COUNTIF(C4:N4,"SI")/6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
@@ -918,14 +937,17 @@
         <v>4</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N5" s="6">
-        <f>COUNTIF(C5:M5,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="6">
+        <f>COUNTIF(C5:N5,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -963,14 +985,17 @@
         <v>4</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N6" s="6">
-        <f>COUNTIF(C6:M6,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" ref="O6:O17" si="0">COUNTIF(C6:N6,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1008,14 +1033,17 @@
         <v>4</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="6">
-        <f>COUNTIF(C7:M7,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1053,19 +1081,22 @@
         <v>4</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N8" s="6">
-        <f>COUNTIF(C8:M8,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1098,14 +1129,17 @@
         <v>4</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="6">
-        <f>COUNTIF(C9:M9,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1143,14 +1177,17 @@
         <v>4</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="6">
-        <f>COUNTIF(C10:M10,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1188,19 +1225,22 @@
         <v>4</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N11" s="6">
-        <f>COUNTIF(C11:M11,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -1233,14 +1273,17 @@
         <v>4</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="6">
-        <f>COUNTIF(C12:M12,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
@@ -1278,14 +1321,17 @@
         <v>4</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N13" s="6">
-        <f>COUNTIF(C13:M13,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1323,14 +1369,17 @@
         <v>4</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="6">
-        <f>COUNTIF(C14:M14,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
@@ -1368,14 +1417,17 @@
         <v>4</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="6">
-        <f>COUNTIF(C15:M15,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
@@ -1413,14 +1465,17 @@
         <v>4</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N16" s="6">
-        <f>COUNTIF(C16:M16,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
@@ -1458,14 +1513,17 @@
         <v>4</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="6">
-        <f>COUNTIF(C17:M17,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -1505,12 +1563,15 @@
       <c r="M18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="6">
-        <f>COUNTIF(C18:M18,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="6">
+        <f>COUNTIF(C18:N18,"SI")/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -1548,14 +1609,17 @@
         <v>4</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N19" s="6">
-        <f>COUNTIF(C19:M19,"SI")/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O19" s="6">
+        <f>COUNTIF(C19:N19,"SI")/9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -1595,12 +1659,15 @@
       <c r="M20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="6">
-        <f>COUNTIF(C20:M20,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="6">
+        <f>COUNTIF(C20:N20,"SI")/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
@@ -1640,12 +1707,15 @@
       <c r="M21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="6">
-        <f>COUNTIF(C21:M21,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" ref="O21:O23" si="1">COUNTIF(C21:N21,"SI")/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -1685,12 +1755,15 @@
       <c r="M22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="6">
-        <f>COUNTIF(C22:M22,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>31</v>
       </c>
@@ -1730,12 +1803,15 @@
       <c r="M23" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N23" s="6">
-        <f>COUNTIF(C23:M23,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>9</v>
       </c>
@@ -1775,12 +1851,15 @@
       <c r="M24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="6">
-        <f>COUNTIF(C24:M24,"SI")/11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N24" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="6">
+        <f>COUNTIF(C24:N24,"SI")/12</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -1818,14 +1897,17 @@
         <v>4</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N25" s="6">
-        <f>COUNTIF(C25:M25,"SI")/10</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" s="6">
+        <f>COUNTIF(C25:N25,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -1865,12 +1947,15 @@
       <c r="M26" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N26" s="6">
-        <f>COUNTIF(C26:M26,"SI")/9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="6">
+        <f>COUNTIF(C26:N26,"SI")/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
@@ -1910,12 +1995,15 @@
       <c r="M27" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N27" s="6">
-        <f>COUNTIF(C27:M27,"SI")/11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="6">
+        <f>COUNTIF(C27:N27,"SI")/12</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>29</v>
       </c>
@@ -1955,12 +2043,15 @@
       <c r="M28" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N28" s="6">
-        <f>COUNTIF(C28:M28,"SI")/11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O28" s="6">
+        <f t="shared" ref="O28:O30" si="2">COUNTIF(C28:N28,"SI")/12</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
@@ -2000,12 +2091,15 @@
       <c r="M29" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N29" s="6">
-        <f>COUNTIF(C29:M29,"SI")/11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N29" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>12</v>
       </c>
@@ -2045,17 +2139,20 @@
       <c r="M30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N30" s="6">
-        <f>COUNTIF(C30:M30,"SI")/11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O30" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -2088,19 +2185,22 @@
         <v>4</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N31" s="6">
-        <f>COUNTIF(C31:M31,"SI")/10</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O31" s="6">
+        <f>COUNTIF(C31:N31,"SI")/11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>11</v>
@@ -2130,22 +2230,25 @@
         <v>4</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="6">
-        <f>COUNTIF(C32:M32,"SI")/5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="6">
+        <f>COUNTIF(C32:N32,"SI")/5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -2178,22 +2281,25 @@
         <v>4</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="6">
-        <f>COUNTIF(C33:M33,"SI")/10</f>
+        <v>4</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="6">
+        <f>COUNTIF(C33:N33,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:N33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:O33">
     <sortCondition ref="B1:B33"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:M33">
+  <conditionalFormatting sqref="C3:N33">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="No aplica">
       <formula>NOT(ISERROR(SEARCH("No aplica",C3)))</formula>
     </cfRule>
@@ -2204,7 +2310,7 @@
       <formula>NOT(ISERROR(SEARCH("SI",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N33">
+  <conditionalFormatting sqref="O3:O33">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>0.85</formula>
     </cfRule>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01BD6C6A-B252-734B-B074-4482B5C3E542}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F595E9-0ECF-A044-8ECE-1D45D2C29940}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="61">
   <si>
     <t>Atleta</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>Diego Jaime</t>
-  </si>
-  <si>
-    <t>COPA ACTION GYM 26</t>
   </si>
   <si>
     <t>AGEPAC 27</t>
@@ -225,6 +222,9 @@
   </si>
   <si>
     <t>SELECTIVO NACIONAL 27</t>
+  </si>
+  <si>
+    <t>COPA ACTION GYM o CDI 26</t>
   </si>
 </sst>
 </file>
@@ -723,40 +723,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
@@ -766,46 +766,46 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
@@ -1096,7 +1096,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1240,7 +1240,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -2152,7 +2152,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -2200,7 +2200,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>11</v>
@@ -2248,7 +2248,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F595E9-0ECF-A044-8ECE-1D45D2C29940}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8EF67A-334A-804C-AC45-72DF28B77307}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="60">
   <si>
     <t>Atleta</t>
   </si>
@@ -838,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>5</v>
@@ -847,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="O3" s="6">
-        <f>COUNTIF(C3:N3,"SI")/6</f>
+        <f>COUNTIF(C3:N3,"SI")/7</f>
         <v>1</v>
       </c>
     </row>
@@ -886,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>5</v>
@@ -895,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="O4" s="6">
-        <f>COUNTIF(C4:N4,"SI")/6</f>
+        <f>COUNTIF(C4:N4,"SI")/7</f>
         <v>1</v>
       </c>
     </row>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8EF67A-334A-804C-AC45-72DF28B77307}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC9A4082-5E00-CF48-87C2-4049FE249827}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
   <si>
     <t>Atleta</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>CAMPEONATO NACIONAL FMG 27</t>
-  </si>
-  <si>
-    <t>OLIMPIADA NACIONAL 27</t>
   </si>
   <si>
     <t>10 FIG</t>
@@ -225,6 +222,13 @@
   </si>
   <si>
     <t>COPA ACTION GYM o CDI 26</t>
+  </si>
+  <si>
+    <t>JUEGOS CONADE ON 27</t>
+  </si>
+  <si>
+    <t>SEDE
+Tamaulipas Tamaulipas</t>
   </si>
 </sst>
 </file>
@@ -723,19 +727,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
@@ -750,13 +754,13 @@
         <v>37</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
@@ -766,46 +770,46 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -853,7 +857,7 @@
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -901,7 +905,7 @@
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
@@ -1096,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1240,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -2152,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -2200,7 +2204,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>11</v>
@@ -2248,7 +2252,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC9A4082-5E00-CF48-87C2-4049FE249827}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3245AA-C63A-234D-91D2-6905E1388B8B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="64">
   <si>
     <t>Atleta</t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>AGEPAC 27</t>
-  </si>
-  <si>
-    <t>2DO SELECTIVO 27</t>
   </si>
   <si>
     <t>COPA JAIME ROMERO 27</t>
@@ -218,9 +215,6 @@
     <t>MIKULAK INVITATIONAL CUP 27</t>
   </si>
   <si>
-    <t>SELECTIVO NACIONAL 27</t>
-  </si>
-  <si>
     <t>COPA ACTION GYM o CDI 26</t>
   </si>
   <si>
@@ -229,6 +223,12 @@
   <si>
     <t>SEDE
 Tamaulipas Tamaulipas</t>
+  </si>
+  <si>
+    <t>PROBABLE 1ER SELECTIVO NACIONAL 27</t>
+  </si>
+  <si>
+    <t>PROBABLE 2DO SELECTIVO NACIONAL 27</t>
   </si>
 </sst>
 </file>
@@ -727,40 +727,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
@@ -770,46 +770,46 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
@@ -995,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="O6" s="6">
-        <f t="shared" ref="O6:O17" si="0">COUNTIF(C6:N6,"SI")/9</f>
+        <f>COUNTIF(C6:N6,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C7:N7,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="O8" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C8:N8,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1139,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="O9" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C9:N9,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="O10" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C10:N10,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C11:N11,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C12:N12,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C13:N13,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         <v>5</v>
       </c>
       <c r="O14" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C14:N14,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C15:N15,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C16:N16,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(C17:N17,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" ref="O21:O23" si="1">COUNTIF(C21:N21,"SI")/10</f>
+        <f>COUNTIF(C21:N21,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
         <v>4</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C22:N22,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
         <v>4</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C23:N23,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="O28" s="6">
-        <f t="shared" ref="O28:O30" si="2">COUNTIF(C28:N28,"SI")/12</f>
+        <f>COUNTIF(C28:N28,"SI")/12</f>
         <v>1</v>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="O29" s="6">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(C29:N29,"SI")/12</f>
         <v>1</v>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(C30:N30,"SI")/12</f>
         <v>1</v>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -2204,7 +2204,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>11</v>
@@ -2252,7 +2252,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3245AA-C63A-234D-91D2-6905E1388B8B}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D2FA84-B281-6542-9ADC-4B653BAE5D11}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
   <si>
     <t>Atleta</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Por definir</t>
   </si>
   <si>
-    <t>CONTROL SIN JUEZ</t>
-  </si>
-  <si>
     <t>COPA DANIEL CORRAL 27</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>PROBABLE 2DO SELECTIVO NACIONAL 27</t>
+  </si>
+  <si>
+    <t>CONTROL INTERNO</t>
   </si>
 </sst>
 </file>
@@ -727,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>35</v>
@@ -754,13 +754,13 @@
         <v>36</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
@@ -797,13 +797,13 @@
         <v>49</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O2" s="4"/>
     </row>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D2FA84-B281-6542-9ADC-4B653BAE5D11}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9FFAD01-F9CD-AA40-91F6-A29953E57DBD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="61">
   <si>
     <t>Atleta</t>
   </si>
@@ -212,9 +212,6 @@
     <t>MIKULAK INVITATIONAL CUP 27</t>
   </si>
   <si>
-    <t>COPA ACTION GYM o CDI 26</t>
-  </si>
-  <si>
     <t>JUEGOS CONADE ON 27</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>CONTROL INTERNO</t>
+  </si>
+  <si>
+    <t>COPA CDI 26</t>
   </si>
 </sst>
 </file>
@@ -419,6 +419,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,16 +714,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.76171875" style="1" customWidth="1"/>
-    <col min="3" max="14" width="12.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.01171875" style="1"/>
+    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="14" width="12.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1640625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -727,25 +731,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>35</v>
@@ -760,13 +764,13 @@
         <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
@@ -803,7 +807,7 @@
         <v>46</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O2" s="4"/>
     </row>
@@ -947,7 +951,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="6">
-        <f>COUNTIF(C5:N5,"SI")/9</f>
+        <f t="shared" ref="O5:O17" si="0">COUNTIF(C5:N5,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -995,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="O6" s="6">
-        <f>COUNTIF(C6:N6,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1043,7 +1047,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="6">
-        <f>COUNTIF(C7:N7,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1091,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="O8" s="6">
-        <f>COUNTIF(C8:N8,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1139,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="O9" s="6">
-        <f>COUNTIF(C9:N9,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1187,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="O10" s="6">
-        <f>COUNTIF(C10:N10,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1235,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="6">
-        <f>COUNTIF(C11:N11,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1283,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="6">
-        <f>COUNTIF(C12:N12,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1331,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="6">
-        <f>COUNTIF(C13:N13,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="O14" s="6">
-        <f>COUNTIF(C14:N14,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1427,7 +1431,7 @@
         <v>5</v>
       </c>
       <c r="O15" s="6">
-        <f>COUNTIF(C15:N15,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1475,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <f>COUNTIF(C16:N16,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1523,7 +1527,7 @@
         <v>5</v>
       </c>
       <c r="O17" s="6">
-        <f>COUNTIF(C17:N17,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1823,7 +1827,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>4</v>
@@ -1859,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="O24" s="6">
-        <f>COUNTIF(C24:N24,"SI")/12</f>
+        <f>COUNTIF(C24:N24,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -1871,7 +1875,7 @@
         <v>9</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>4</v>
@@ -1907,7 +1911,7 @@
         <v>5</v>
       </c>
       <c r="O25" s="6">
-        <f>COUNTIF(C25:N25,"SI")/11</f>
+        <f>COUNTIF(C25:N25,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -1919,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>4</v>
@@ -1955,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="O26" s="6">
-        <f>COUNTIF(C26:N26,"SI")/10</f>
+        <f>COUNTIF(C26:N26,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1967,7 +1971,7 @@
         <v>9</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>4</v>
@@ -2003,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="O27" s="6">
-        <f>COUNTIF(C27:N27,"SI")/12</f>
+        <f>COUNTIF(C27:N27,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2015,7 +2019,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>4</v>
@@ -2051,7 +2055,7 @@
         <v>4</v>
       </c>
       <c r="O28" s="6">
-        <f>COUNTIF(C28:N28,"SI")/12</f>
+        <f>COUNTIF(C28:N28,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2063,7 +2067,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>4</v>
@@ -2099,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="O29" s="6">
-        <f>COUNTIF(C29:N29,"SI")/12</f>
+        <f>COUNTIF(C29:N29,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2111,7 +2115,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>4</v>
@@ -2147,7 +2151,7 @@
         <v>4</v>
       </c>
       <c r="O30" s="6">
-        <f>COUNTIF(C30:N30,"SI")/12</f>
+        <f>COUNTIF(C30:N30,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2159,7 +2163,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>4</v>
@@ -2195,7 +2199,7 @@
         <v>5</v>
       </c>
       <c r="O31" s="6">
-        <f>COUNTIF(C31:N31,"SI")/11</f>
+        <f>COUNTIF(C31:N31,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -2255,7 +2259,7 @@
         <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>4</v>
@@ -2291,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="O33" s="6">
-        <f>COUNTIF(C33:N33,"SI")/11</f>
+        <f>COUNTIF(C33:N33,"SI")/10</f>
         <v>1</v>
       </c>
     </row>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9FFAD01-F9CD-AA40-91F6-A29953E57DBD}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{914884E5-ECDF-FA4A-89CA-EFA33A6755B4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
   <si>
     <t>Atleta</t>
   </si>
@@ -162,10 +162,6 @@
   </si>
   <si>
     <t>Erik Lopez</t>
-  </si>
-  <si>
-    <t>SEDE
-Tlaxcala Tlaxcala</t>
   </si>
   <si>
     <t>SEDE
@@ -229,6 +225,10 @@
   </si>
   <si>
     <t>COPA CDI 26</t>
+  </si>
+  <si>
+    <t>SEDE
+Ciudad de Mexico Centro Deportivo Israelita</t>
   </si>
 </sst>
 </file>
@@ -419,10 +419,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -714,16 +710,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="14" width="12.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1640625" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="10.89453125" style="1" customWidth="1"/>
+    <col min="3" max="14" width="12.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.01171875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -731,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>35</v>
@@ -758,56 +754,56 @@
         <v>36</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O2" s="4"/>
     </row>
@@ -1104,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1248,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>

--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{914884E5-ECDF-FA4A-89CA-EFA33A6755B4}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7543BAEC-C356-8846-BD0B-318429B8DDDD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="61">
   <si>
     <t>Atleta</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>Diego Jaime</t>
-  </si>
-  <si>
-    <t>AGEPAC 27</t>
   </si>
   <si>
     <t>COPA JAIME ROMERO 27</t>
@@ -181,10 +178,6 @@
   </si>
   <si>
     <t>SEDE
-Puebla Puebla</t>
-  </si>
-  <si>
-    <t>SEDE
 Guadalajara Jalisco</t>
   </si>
   <si>
@@ -229,6 +222,13 @@
   <si>
     <t>SEDE
 Ciudad de Mexico Centro Deportivo Israelita</t>
+  </si>
+  <si>
+    <t>COPA BKA 27</t>
+  </si>
+  <si>
+    <t>SEDE
+Leon Guanajuato</t>
   </si>
 </sst>
 </file>
@@ -710,16 +710,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.89453125" style="1" customWidth="1"/>
-    <col min="3" max="14" width="12.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.01171875" style="1"/>
+    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="14" width="12.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1640625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -727,89 +727,89 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
@@ -1100,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1244,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -2156,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>11</v>
@@ -2204,7 +2204,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>11</v>
@@ -2252,7 +2252,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>11</v>
